--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484574_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484574_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. MONTILLA GONZALEZ</t>
+          <t>J. SOSA GONZALEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1072</v>
+        <v>3.1558</v>
       </c>
       <c r="E2" t="n">
-        <v>1.8819</v>
+        <v>1.1406</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2254</v>
+        <v>2.0152</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.1251</v>
+        <v>1.9075</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.1666</v>
+        <v>-1.8626</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0416</v>
+        <v>3.7701</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.1082</v>
+        <v>2.3077</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.3165</v>
+        <v>0.2043</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2084</v>
+        <v>2.1034</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.0169</v>
+        <v>-0.4002</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.8501</v>
+        <v>-2.0668</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8332000000000001</v>
+        <v>1.6667</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.733</v>
+        <v>-1.6493</v>
       </c>
       <c r="Q2" t="n">
         <v>-3.6651</v>
       </c>
       <c r="R2" t="n">
-        <v>2.9321</v>
+        <v>2.0158</v>
       </c>
       <c r="S2" t="n">
-        <v>4.7325</v>
+        <v>1.6307</v>
       </c>
       <c r="T2" t="n">
-        <v>3.4224</v>
+        <v>0.9092</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3101</v>
+        <v>0.7215</v>
       </c>
       <c r="V2" t="n">
-        <v>2.2328</v>
+        <v>1.267</v>
       </c>
       <c r="W2" t="n">
-        <v>2.2328</v>
+        <v>1.5889</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8964</v>
+        <v>3.0261</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7722</v>
+        <v>1.5799</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1242</v>
+        <v>1.4462</v>
       </c>
       <c r="G3" t="n">
         <v>1.4817</v>
@@ -688,13 +688,13 @@
         <v>2.1991</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1031</v>
+        <v>0.2329</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4744</v>
+        <v>0.2821</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3713</v>
+        <v>-0.0492</v>
       </c>
       <c r="V3" t="n">
         <v>0.945</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. SOSA GONZALEZ</t>
+          <t>J. ARNAIZ VEGA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8866</v>
+        <v>2.8767</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7971</v>
+        <v>0.7862</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0895</v>
+        <v>2.0905</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9075</v>
+        <v>0.6324</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.8626</v>
+        <v>-1.8585</v>
       </c>
       <c r="I4" t="n">
-        <v>3.7701</v>
+        <v>2.4909</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3077</v>
+        <v>1.2142</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2043</v>
+        <v>-0.796</v>
       </c>
       <c r="L4" t="n">
-        <v>2.1034</v>
+        <v>2.0102</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4002</v>
+        <v>-0.5818</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.0668</v>
+        <v>-1.0624</v>
       </c>
       <c r="O4" t="n">
-        <v>1.6667</v>
+        <v>0.4807</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.6493</v>
+        <v>0.733</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.6651</v>
+        <v>-0.9163</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0158</v>
+        <v>1.6493</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3615</v>
+        <v>0.8882</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5656</v>
+        <v>0.4883</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7958</v>
+        <v>0.3999</v>
       </c>
       <c r="V4" t="n">
-        <v>1.267</v>
+        <v>0.6231</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5889</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3219</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. GONZALEZ SOLER</t>
+          <t>J. MONTILLA GONZALEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3642</v>
+        <v>2.6694</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5871</v>
+        <v>0.0138</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7771</v>
+        <v>2.6556</v>
       </c>
       <c r="G5" t="n">
-        <v>3.0787</v>
+        <v>-1.1251</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0147</v>
+        <v>-2.1666</v>
       </c>
       <c r="I5" t="n">
-        <v>3.0934</v>
+        <v>1.0416</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7614</v>
+        <v>-0.1082</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6936</v>
+        <v>-0.3165</v>
       </c>
       <c r="L5" t="n">
-        <v>2.0678</v>
+        <v>0.2084</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3173</v>
+        <v>-1.0169</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7083</v>
+        <v>-1.8501</v>
       </c>
       <c r="O5" t="n">
-        <v>1.0256</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.2828</v>
+        <v>-0.733</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.8326</v>
+        <v>-3.6651</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5498</v>
+        <v>2.9321</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2018</v>
+        <v>2.2947</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9698</v>
+        <v>1.5543</v>
       </c>
       <c r="U5" t="n">
-        <v>0.232</v>
+        <v>0.7403</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6335</v>
+        <v>2.2328</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3115</v>
+        <v>2.2328</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. ARNAIZ VEGA</t>
+          <t>A. GONZALEZ SOLER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7447</v>
+        <v>1.9415</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2715</v>
+        <v>1.0652</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0162</v>
+        <v>0.8762</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6324</v>
+        <v>3.0787</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.8585</v>
+        <v>-0.0147</v>
       </c>
       <c r="I6" t="n">
-        <v>2.4909</v>
+        <v>3.0934</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2142</v>
+        <v>2.7614</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.796</v>
+        <v>0.6936</v>
       </c>
       <c r="L6" t="n">
-        <v>2.0102</v>
+        <v>2.0678</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5818</v>
+        <v>0.3173</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0624</v>
+        <v>-0.7083</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4807</v>
+        <v>1.0256</v>
       </c>
       <c r="P6" t="n">
-        <v>0.733</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6493</v>
+        <v>0.5498</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2438</v>
+        <v>0.779</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5694</v>
+        <v>0.448</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3256</v>
+        <v>0.3311</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6231</v>
+        <v>-0.6335</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.3115</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6231</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0796</v>
+        <v>0.8898</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.537</v>
+        <v>-1.5781</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6166</v>
+        <v>2.4679</v>
       </c>
       <c r="G7" t="n">
         <v>-1.3529</v>
@@ -1000,13 +1000,13 @@
         <v>1.8326</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8722</v>
+        <v>0.6825</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3643</v>
+        <v>0.3232</v>
       </c>
       <c r="U7" t="n">
-        <v>0.508</v>
+        <v>0.3593</v>
       </c>
       <c r="V7" t="n">
         <v>0.6439</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7372</v>
+        <v>0.8581</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6259</v>
+        <v>0.7221</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1112</v>
+        <v>0.136</v>
       </c>
       <c r="G8" t="n">
         <v>-0.7296</v>
@@ -1078,13 +1078,13 @@
         <v>0.1833</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0165</v>
+        <v>0.1374</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0165</v>
+        <v>0.0413</v>
       </c>
       <c r="V8" t="n">
         <v>1.267</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6523</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4372</v>
+        <v>-0.6294999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0894</v>
+        <v>1.1885</v>
       </c>
       <c r="G9" t="n">
         <v>-0.3663</v>
@@ -1156,13 +1156,13 @@
         <v>0.5498</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4688</v>
+        <v>0.3756</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3839</v>
+        <v>0.1916</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0849</v>
+        <v>0.184</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. YUBERO OJEDA</t>
+          <t>B. FOS CERVERA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3425</v>
+        <v>-0.1096</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7457</v>
+        <v>-0.4902</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4032</v>
+        <v>0.3806</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.059</v>
+        <v>-1.092</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4918</v>
+        <v>-0.3002</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4328</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0662</v>
+        <v>-0.4476</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.217</v>
+        <v>0.1517</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1508</v>
+        <v>-0.5994</v>
       </c>
       <c r="M10" t="n">
-        <v>1.0072</v>
+        <v>-0.6443</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2748</v>
+        <v>-0.4519</v>
       </c>
       <c r="O10" t="n">
-        <v>1.2821</v>
+        <v>-0.1925</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3665</v>
+        <v>2.0158</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5498</v>
+        <v>2.0158</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7165</v>
+        <v>-0.0781</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2368</v>
+        <v>-0.0426</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4797</v>
+        <v>-0.0355</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6335</v>
+        <v>-0.9554</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6335</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B. FOS CERVERA</t>
+          <t>J. YUBERO OJEDA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7827</v>
+        <v>-0.3122</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1633</v>
+        <v>-1.6907</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3806</v>
+        <v>1.3785</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.092</v>
+        <v>-0.059</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3002</v>
+        <v>-1.4918</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7917999999999999</v>
+        <v>1.4328</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4476</v>
+        <v>-1.0662</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1517</v>
+        <v>-1.217</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5994</v>
+        <v>0.1508</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6443</v>
+        <v>1.0072</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4519</v>
+        <v>-0.2748</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1925</v>
+        <v>1.2821</v>
       </c>
       <c r="P11" t="n">
-        <v>2.0158</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0158</v>
+        <v>0.5498</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7511</v>
+        <v>0.7468</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7157</v>
+        <v>0.2919</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0355</v>
+        <v>0.4549</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9554</v>
+        <v>-0.6335</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.9554</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9954</v>
+        <v>-3.2343</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.5126</v>
+        <v>-3.801</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5172</v>
+        <v>0.5667</v>
       </c>
       <c r="G12" t="n">
         <v>-2.2946</v>
@@ -1390,13 +1390,13 @@
         <v>0.733</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3988</v>
+        <v>0.1599</v>
       </c>
       <c r="T12" t="n">
-        <v>0.494</v>
+        <v>0.2055</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.09520000000000001</v>
+        <v>-0.0456</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.4022</v>
+        <v>-5.0998</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.3445</v>
+        <v>-6.1906</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9422</v>
+        <v>1.0908</v>
       </c>
       <c r="G13" t="n">
         <v>-6.4672</v>
@@ -1468,13 +1468,13 @@
         <v>2.1991</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6339</v>
+        <v>0.6686</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6976</v>
+        <v>0.4563</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0636</v>
+        <v>0.2123</v>
       </c>
       <c r="V13" t="n">
         <v>0.3324</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.9454</v>
+        <v>7.220499999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-9.3476</v>
+        <v>-9.0723</v>
       </c>
       <c r="F14" t="n">
-        <v>16.2928</v>
+        <v>16.2927</v>
       </c>
       <c r="G14" t="n">
         <v>-6.3864</v>
@@ -1546,13 +1546,13 @@
         <v>17.4095</v>
       </c>
       <c r="S14" t="n">
-        <v>8.242900000000001</v>
+        <v>8.5182</v>
       </c>
       <c r="T14" t="n">
-        <v>4.9285</v>
+        <v>5.204</v>
       </c>
       <c r="U14" t="n">
-        <v>3.3142</v>
+        <v>3.3143</v>
       </c>
       <c r="V14" t="n">
         <v>5.0888</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2803</v>
+        <v>1.0034</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3537</v>
+        <v>0.9691</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0735</v>
+        <v>0.0343</v>
       </c>
       <c r="G15" t="n">
         <v>3.1452</v>
@@ -1624,13 +1624,13 @@
         <v>2.0158</v>
       </c>
       <c r="S15" t="n">
-        <v>0.048</v>
+        <v>-0.2289</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3092</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2613</v>
+        <v>-0.1535</v>
       </c>
       <c r="V15" t="n">
         <v>-1.9129</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.774</v>
       </c>
       <c r="E16" t="n">
         <v>-1.5213</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0389</v>
+        <v>2.2953</v>
       </c>
       <c r="G16" t="n">
         <v>2.1526</v>
@@ -1702,13 +1702,13 @@
         <v>2.3823</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2089</v>
+        <v>-0.9525</v>
       </c>
       <c r="T16" t="n">
         <v>-0.4419</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.767</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>-1.8921</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. CARRION BALLESTER</t>
+          <t>D. OLID SANGUESA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4469</v>
+        <v>0.253</v>
       </c>
       <c r="E17" t="n">
-        <v>0.453</v>
+        <v>-0.7617</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0061</v>
+        <v>1.0147</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.351</v>
+        <v>-0.3657</v>
       </c>
       <c r="H17" t="n">
-        <v>2.4058</v>
+        <v>-0.1411</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.7569</v>
+        <v>-0.2246</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0677</v>
+        <v>-0.4676</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3497</v>
+        <v>-0.4676</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.2821</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4187</v>
+        <v>0.102</v>
       </c>
       <c r="N17" t="n">
-        <v>1.0561</v>
+        <v>0.3265</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4748</v>
+        <v>-0.2246</v>
       </c>
       <c r="P17" t="n">
         <v>0.733</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0995</v>
+        <v>-0.1833</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8326</v>
+        <v>0.9163</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6984</v>
+        <v>-0.4259</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5294</v>
+        <v>-0.1108</v>
       </c>
       <c r="U17" t="n">
-        <v>0.169</v>
+        <v>-0.3151</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6335</v>
+        <v>0.3115</v>
       </c>
       <c r="W17" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.5889</v>
+        <v>0.3115</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. HORTELANO ESCRIBA</t>
+          <t>H. MARI LOPEZ-ROCA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0004</v>
+        <v>0.1826</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9921</v>
+        <v>-1.5685</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9925</v>
+        <v>1.7511</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9401</v>
+        <v>1.4592</v>
       </c>
       <c r="H18" t="n">
-        <v>2.2126</v>
+        <v>2.155</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2725</v>
+        <v>-0.6957</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4552</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>1.7274</v>
+        <v>1.5323</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2722</v>
+        <v>-0.5994</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4849</v>
+        <v>0.5262</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4852</v>
+        <v>0.6226</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0003</v>
+        <v>-0.0964</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.733</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9321</v>
+        <v>-2.7489</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1991</v>
+        <v>1.4661</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1069</v>
+        <v>-0.6273</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5294</v>
+        <v>-0.3861</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4225</v>
+        <v>-0.2412</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3136</v>
+        <v>0.6335</v>
       </c>
       <c r="W18" t="n">
-        <v>0.9554</v>
+        <v>0.6335</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2691</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3236</v>
+        <v>-0.1458</v>
       </c>
       <c r="E19" t="n">
         <v>-0.6744</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3508</v>
+        <v>0.5286</v>
       </c>
       <c r="G19" t="n">
         <v>-0.54</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4066</v>
+        <v>-0.2289</v>
       </c>
       <c r="T19" t="n">
         <v>-0.0551</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3516</v>
+        <v>-0.1738</v>
       </c>
       <c r="V19" t="n">
         <v>0.6231</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>H. MARI LOPEZ-ROCA</t>
+          <t>A. CARRION BALLESTER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4336</v>
+        <v>-0.1781</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9531</v>
+        <v>-0.0278</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5195</v>
+        <v>-0.1504</v>
       </c>
       <c r="G20" t="n">
-        <v>1.4592</v>
+        <v>-0.351</v>
       </c>
       <c r="H20" t="n">
-        <v>2.155</v>
+        <v>2.4058</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6957</v>
+        <v>-2.7569</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.0677</v>
       </c>
       <c r="K20" t="n">
-        <v>1.5323</v>
+        <v>1.3497</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5994</v>
+        <v>-1.2821</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5262</v>
+        <v>-0.4187</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6226</v>
+        <v>1.0561</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0964</v>
+        <v>-1.4748</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.2828</v>
+        <v>0.733</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.7489</v>
+        <v>-1.0995</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4661</v>
+        <v>1.8326</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2435</v>
+        <v>0.0733</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7707000000000001</v>
+        <v>0.0487</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4728</v>
+        <v>0.0247</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6335</v>
+        <v>-0.6335</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6335</v>
+        <v>0.9554</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. OLID SANGUESA</t>
+          <t>C. HORTELANO ESCRIBA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5323</v>
+        <v>-0.4542</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1464</v>
+        <v>-1.3767</v>
       </c>
       <c r="F21" t="n">
-        <v>0.614</v>
+        <v>0.9225</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3657</v>
+        <v>0.9401</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1411</v>
+        <v>2.2126</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2246</v>
+        <v>-1.2725</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4676</v>
+        <v>0.4552</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4676</v>
+        <v>1.7274</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-1.2722</v>
       </c>
       <c r="M21" t="n">
-        <v>0.102</v>
+        <v>0.4849</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3265</v>
+        <v>0.4852</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2246</v>
+        <v>-0.0003</v>
       </c>
       <c r="P21" t="n">
-        <v>0.733</v>
+        <v>-0.733</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.1833</v>
+        <v>-2.9321</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9163</v>
+        <v>2.1991</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2112</v>
+        <v>-0.3477</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4955</v>
+        <v>0.1448</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7158</v>
+        <v>-0.4925</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3115</v>
+        <v>-0.3136</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3115</v>
+        <v>-1.2691</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.8159999999999999</v>
+        <v>-0.5567</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9614</v>
+        <v>-3.0576</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1454</v>
+        <v>2.5009</v>
       </c>
       <c r="G22" t="n">
         <v>-0.0919</v>
@@ -2170,13 +2170,13 @@
         <v>2.3823</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2718</v>
+        <v>-1.0124</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.552</v>
+        <v>-0.6482</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7198</v>
+        <v>-0.3643</v>
       </c>
       <c r="V22" t="n">
         <v>-0.0021</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.3824</v>
+        <v>-1.2149</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0805</v>
+        <v>-1.8882</v>
       </c>
       <c r="F23" t="n">
-        <v>0.698</v>
+        <v>0.6732</v>
       </c>
       <c r="G23" t="n">
         <v>0.5134</v>
@@ -2248,13 +2248,13 @@
         <v>1.2828</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7126</v>
+        <v>-0.5451</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6606</v>
+        <v>-0.4683</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.052</v>
+        <v>-0.0767</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6335</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.6988</v>
+        <v>-1.2514</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.2386</v>
+        <v>-2.1425</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5399</v>
+        <v>0.891</v>
       </c>
       <c r="G24" t="n">
         <v>-1.462</v>
@@ -2326,13 +2326,13 @@
         <v>1.0995</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3363</v>
+        <v>-0.8889</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.6746</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5655</v>
+        <v>-0.2144</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.0038</v>
+        <v>-3.4341</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.5318</v>
+        <v>-4.2433</v>
       </c>
       <c r="F25" t="n">
-        <v>0.528</v>
+        <v>0.8092</v>
       </c>
       <c r="G25" t="n">
         <v>0.9863</v>
@@ -2404,13 +2404,13 @@
         <v>1.8326</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.7052</v>
+        <v>-1.1356</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9359</v>
+        <v>-0.6474</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7693</v>
+        <v>-0.4881</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2691</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.9453</v>
+        <v>-5.0222</v>
       </c>
       <c r="E26" t="n">
         <v>-16.2929</v>
       </c>
       <c r="F26" t="n">
-        <v>9.3474</v>
+        <v>11.2704</v>
       </c>
       <c r="G26" t="n">
         <v>6.386200000000001</v>
@@ -2461,7 +2461,7 @@
         <v>10.1817</v>
       </c>
       <c r="L26" t="n">
-        <v>-7.371099999999999</v>
+        <v>-7.3711</v>
       </c>
       <c r="M26" t="n">
         <v>3.5753</v>
@@ -2482,13 +2482,13 @@
         <v>17.4094</v>
       </c>
       <c r="S26" t="n">
-        <v>-8.242800000000001</v>
+        <v>-6.319900000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.3144</v>
+        <v>-3.3143</v>
       </c>
       <c r="U26" t="n">
-        <v>-4.9286</v>
+        <v>-3.005500000000001</v>
       </c>
       <c r="V26" t="n">
         <v>-5.088699999999999</v>
